--- a/lab_schedule.xlsx
+++ b/lab_schedule.xlsx
@@ -1,26 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sylva\Dropbox\erasmus\course\ht2_tddd07-real_time_systems\TDDD07-Real_Time_Systems_Labs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{451D355E-C95E-475A-AD2C-2CAA843664F5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A187AA-5F2D-419A-9708-E2145D68878B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="27930" windowHeight="16440" xr2:uid="{42DEF2D1-7947-46AB-B1AA-24ABCB262B64}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuil1 (4)" sheetId="4" r:id="rId1"/>
+    <sheet name="Feuil1 (3)" sheetId="3" r:id="rId2"/>
+    <sheet name="Feuil1 (2)" sheetId="2" r:id="rId3"/>
+    <sheet name="Feuil1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Feuil1!$B$4:$D$4</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Feuil1!$E$4</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Feuil1!$B$2:$D$2</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Feuil1!$E$2</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,12 +34,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="11">
   <si>
     <t>Task</t>
-  </si>
-  <si>
-    <t>Begin time</t>
   </si>
   <si>
     <t>End time</t>
@@ -64,6 +58,15 @@
   </si>
   <si>
     <t>Idle</t>
+  </si>
+  <si>
+    <t>Start time</t>
+  </si>
+  <si>
+    <t>Report</t>
+  </si>
+  <si>
+    <t>Control</t>
   </si>
 </sst>
 </file>
@@ -99,11 +102,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -124,7 +128,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -192,7 +196,3859 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="3.1175338376820544E-2"/>
+          <c:y val="0.13497371188222926"/>
+          <c:w val="0.81086387730945397"/>
+          <c:h val="0.65020657906720647"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Feuil1 (4)'!$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Communicate</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (4)'!$C$4:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (4)'!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (4)'!$C$5:$E$5</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (4)'!$E$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6303-462E-A32C-27CDD55656E5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Feuil1 (4)'!$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Refine</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (4)'!$C$4:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (4)'!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (4)'!$C$6:$E$6</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (4)'!$E$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6303-462E-A32C-27CDD55656E5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Feuil1 (4)'!$B$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Report</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (4)'!$C$4:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (4)'!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (4)'!$C$7:$E$7</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (4)'!$E$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-6303-462E-A32C-27CDD55656E5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Feuil1 (4)'!$B$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Mission</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (4)'!$C$4:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (4)'!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (4)'!$C$8:$E$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (4)'!$E$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-6303-462E-A32C-27CDD55656E5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Feuil1 (4)'!$B$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Control</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (4)'!$C$4:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (4)'!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (4)'!$C$9:$E$9</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (4)'!$E$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>24</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-6303-462E-A32C-27CDD55656E5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Feuil1 (4)'!$B$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Avoid</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (4)'!$C$4:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (4)'!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (4)'!$C$10:$E$10</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (4)'!$E$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>23</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-6303-462E-A32C-27CDD55656E5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Feuil1 (4)'!$B$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Navigate</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (4)'!$C$4:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (4)'!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (4)'!$C$11:$E$11</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (4)'!$E$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:categoryFilterExceptions>
+                <c15:categoryFilterException>
+                  <c15:sqref>'Feuil1 (4)'!$C$11</c15:sqref>
+                  <c15:invertIfNegative val="0"/>
+                  <c15:bubble3D val="0"/>
+                </c15:categoryFilterException>
+              </c15:categoryFilterExceptions>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-6303-462E-A32C-27CDD55656E5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Feuil1 (4)'!$B$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Idle</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (4)'!$C$4:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (4)'!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (4)'!$C$12:$E$12</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (4)'!$E$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>35</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-6303-462E-A32C-27CDD55656E5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="65324912"/>
+        <c:axId val="969604336"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="65324912"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="969604336"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="969604336"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="65324912"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.11900921208378365"/>
+          <c:y val="0.90378499217566255"/>
+          <c:w val="0.47178549740106018"/>
+          <c:h val="7.0978414764400505E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Minor Cycle 1</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="3.1175338376820544E-2"/>
+          <c:y val="0.13497371188222926"/>
+          <c:w val="0.81086387730945397"/>
+          <c:h val="0.65020657906720647"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Feuil1 (3)'!$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Communicate</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (3)'!$C$4:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (3)'!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (3)'!$C$5:$E$5</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (3)'!$E$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4F03-49A7-8866-BB2222AB8B50}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Feuil1 (3)'!$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Refine</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (3)'!$C$4:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (3)'!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (3)'!$C$6:$E$6</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (3)'!$E$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4F03-49A7-8866-BB2222AB8B50}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Feuil1 (3)'!$B$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Report</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (3)'!$C$4:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (3)'!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (3)'!$C$7:$E$7</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (3)'!$E$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-4F03-49A7-8866-BB2222AB8B50}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Feuil1 (3)'!$B$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Mission</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (3)'!$C$4:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (3)'!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (3)'!$C$8:$E$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (3)'!$E$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-4F03-49A7-8866-BB2222AB8B50}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Feuil1 (3)'!$B$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Control</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (3)'!$C$4:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (3)'!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (3)'!$C$9:$E$9</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (3)'!$E$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-4F03-49A7-8866-BB2222AB8B50}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Feuil1 (3)'!$B$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Avoid</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (3)'!$C$4:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (3)'!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (3)'!$C$10:$E$10</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (3)'!$E$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>23</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-4F03-49A7-8866-BB2222AB8B50}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Feuil1 (3)'!$B$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Navigate</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (3)'!$C$4:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (3)'!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (3)'!$C$11:$E$11</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (3)'!$E$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:categoryFilterExceptions>
+                <c15:categoryFilterException>
+                  <c15:sqref>'Feuil1 (3)'!$C$11</c15:sqref>
+                  <c15:invertIfNegative val="0"/>
+                  <c15:bubble3D val="0"/>
+                </c15:categoryFilterException>
+              </c15:categoryFilterExceptions>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-4F03-49A7-8866-BB2222AB8B50}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Feuil1 (3)'!$B$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Idle</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (3)'!$C$4:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (3)'!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (3)'!$C$12:$E$12</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (3)'!$E$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>59</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-4F03-49A7-8866-BB2222AB8B50}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="65324912"/>
+        <c:axId val="969604336"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="65324912"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="969604336"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="969604336"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="65324912"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.11639483299881632"/>
+          <c:y val="0.88696059680237127"/>
+          <c:w val="0.47178549740106018"/>
+          <c:h val="7.0978414764400505E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Minor Cycle 1</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="3.1175338376820544E-2"/>
+          <c:y val="0.13497371188222926"/>
+          <c:w val="0.81086387730945397"/>
+          <c:h val="0.65020657906720647"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Feuil1 (2)'!$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Communicate</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (2)'!$C$4:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (2)'!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (2)'!$C$5:$E$5</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (2)'!$E$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-435A-4E9B-97B1-E87A97A20CF4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Feuil1 (2)'!$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Refine</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (2)'!$C$4:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (2)'!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (2)'!$C$6:$E$6</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (2)'!$E$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-435A-4E9B-97B1-E87A97A20CF4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Feuil1 (2)'!$B$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Report</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (2)'!$C$4:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (2)'!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (2)'!$C$7:$E$7</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (2)'!$E$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-435A-4E9B-97B1-E87A97A20CF4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Feuil1 (2)'!$B$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Mission</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (2)'!$C$4:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (2)'!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (2)'!$C$8:$E$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (2)'!$E$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-435A-4E9B-97B1-E87A97A20CF4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Feuil1 (2)'!$B$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Control</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (2)'!$C$4:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (2)'!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (2)'!$C$9:$E$9</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (2)'!$E$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-435A-4E9B-97B1-E87A97A20CF4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Feuil1 (2)'!$B$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Avoid</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (2)'!$C$4:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (2)'!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (2)'!$C$10:$E$10</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (2)'!$E$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>23</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-435A-4E9B-97B1-E87A97A20CF4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Feuil1 (2)'!$B$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Navigate</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (2)'!$C$4:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (2)'!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (2)'!$C$11:$E$11</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (2)'!$E$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:categoryFilterExceptions>
+                <c15:categoryFilterException>
+                  <c15:sqref>'Feuil1 (2)'!$C$11</c15:sqref>
+                  <c15:invertIfNegative val="0"/>
+                  <c15:bubble3D val="0"/>
+                </c15:categoryFilterException>
+              </c15:categoryFilterExceptions>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-435A-4E9B-97B1-E87A97A20CF4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Feuil1 (2)'!$B$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Idle</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (2)'!$C$4:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (2)'!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Feuil1 (2)'!$C$12:$E$12</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Feuil1 (2)'!$E$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-435A-4E9B-97B1-E87A97A20CF4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="65324912"/>
+        <c:axId val="969604336"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="65324912"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="969604336"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="969604336"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="65324912"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Minor Cycle 1</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="3.1175338376820544E-2"/>
+          <c:y val="0.13497371188222926"/>
+          <c:w val="0.81086387730945397"/>
+          <c:h val="0.65020657906720647"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="bar"/>
         <c:grouping val="stacked"/>
@@ -206,7 +4062,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Mission</c:v>
+                  <c:v>Communicate</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -308,7 +4164,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -328,7 +4184,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Navigate</c:v>
+                  <c:v>Refine</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -430,7 +4286,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -450,7 +4306,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Communicate</c:v>
+                  <c:v>Report</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -552,7 +4408,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>8</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -572,7 +4428,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Avoid</c:v>
+                  <c:v>Mission</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -674,7 +4530,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>8</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -694,7 +4550,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Refine</c:v>
+                  <c:v>Control</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -796,7 +4652,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>12</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -918,7 +4774,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>12</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -938,7 +4794,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Idle</c:v>
+                  <c:v>Navigate</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1040,7 +4896,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>58</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1057,6 +4913,130 @@
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000006-7C49-40CF-9774-426E3EA97CD7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Feuil1!$B$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Idle</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Feuil1!$C$4:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Feuil1!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Feuil1!$C$12:$E$12</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Feuil1!$E$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>26</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9E42-44A8-A9B4-E8FCA2399ED0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1304,6 +5284,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
@@ -1809,7 +5909,1651 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>152399</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123824</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Graphique 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0A261A5-0D58-4917-84D3-64CF2B1910AE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>152399</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123824</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Graphique 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25CEBF73-7B22-4271-964A-F1CE9AF1FB8E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>152399</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123824</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Graphique 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B5B2B8D-A0BF-497C-BA8E-BB0A546C714D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -1851,7 +7595,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2146,9 +7890,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2A8A55B-6E7B-4715-B66F-1F7D89955144}">
-  <dimension ref="B2:F11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD2A74C5-D824-4575-9EB3-7234EF891A55}">
+  <dimension ref="B2:F12"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
@@ -2162,109 +7906,600 @@
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>2</v>
       </c>
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
+        <f>E5-C5</f>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <f>D5</f>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
+        <f>E6+C6</f>
+        <v>15</v>
+      </c>
+      <c r="E6" s="2">
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <f t="shared" ref="C7:C12" si="0">D6</f>
+        <v>15</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <f t="shared" ref="D7:D11" si="1">E7+C7</f>
+        <v>16</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="D8">
-        <v>18</v>
+        <f t="shared" si="1"/>
+        <v>17</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C9">
-        <v>18</v>
+        <f t="shared" si="0"/>
+        <v>17</v>
       </c>
       <c r="D9">
-        <v>30</v>
+        <f t="shared" si="1"/>
+        <v>41</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10">
-        <v>30</v>
+        <f t="shared" si="0"/>
+        <v>41</v>
       </c>
       <c r="D10">
-        <v>42</v>
+        <f t="shared" si="1"/>
+        <v>64</v>
       </c>
       <c r="E10">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="D12">
+        <v>100</v>
+      </c>
+      <c r="E12">
+        <f>D12-C12</f>
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46CC260C-2774-441D-B19E-52BE8118B766}">
+  <dimension ref="B2:F12"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F2" s="1"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <f>E5-C5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <f>D5</f>
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <f>E6+C6</f>
+        <v>15</v>
+      </c>
+      <c r="E6" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <f t="shared" ref="C7:C12" si="0">D6</f>
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <f t="shared" ref="D7:D11" si="1">E7+C7</f>
+        <v>16</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="E10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
       <c r="C11">
-        <v>42</v>
+        <f t="shared" si="0"/>
+        <v>40</v>
       </c>
       <c r="D11">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="D12">
         <v>100</v>
       </c>
+      <c r="E12">
+        <f>D12-C12</f>
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E1640B5-5035-4FDF-BF33-57FDBAC93DEE}">
+  <dimension ref="B2:F12"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F2" s="1"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <f>E5-C5</f>
+        <v>9</v>
+      </c>
+      <c r="E5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <f>D5</f>
+        <v>9</v>
+      </c>
+      <c r="D6">
+        <f>E6+C6</f>
+        <v>24</v>
+      </c>
+      <c r="E6" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <f t="shared" ref="C7:C12" si="0">D6</f>
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <f t="shared" ref="D7:D11" si="1">E7+C7</f>
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="E10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
       <c r="E11">
-        <v>58</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="D12">
+        <v>100</v>
+      </c>
+      <c r="E12">
+        <f>D12-C12</f>
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2A8A55B-6E7B-4715-B66F-1F7D89955144}">
+  <dimension ref="B2:F12"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F2" s="1"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <f>E5-C5</f>
+        <v>9</v>
+      </c>
+      <c r="E5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <f>D5</f>
+        <v>9</v>
+      </c>
+      <c r="D6">
+        <f>E6+C6</f>
+        <v>24</v>
+      </c>
+      <c r="E6" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <f t="shared" ref="C7:C12" si="0">D6</f>
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <f t="shared" ref="D7:D11" si="1">E7+C7</f>
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="E9">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+      <c r="E10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>73</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+      <c r="D12">
+        <v>100</v>
+      </c>
+      <c r="E12">
+        <f>D12-C12</f>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
